--- a/InputData/plcy-schd/NBFYIbFP/Non BAU First Year Impacted by Future Policies.xlsx
+++ b/InputData/plcy-schd/NBFYIbFP/Non BAU First Year Impacted by Future Policies.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\plcy-schd\NBFYIbFP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\plcy-schd\NBFYIbFP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573438E3-9D6E-4879-A304-B50D8440B2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CECA5E-9BB7-48E1-9E30-E94D32BE77DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="FYIbFP" sheetId="2" r:id="rId2"/>
+    <sheet name="NBFYIbFP" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
